--- a/Data/t16.2.xlsx
+++ b/Data/t16.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,7 +1153,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1163,17 +1163,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>96.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1183,17 +1183,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>33</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.6</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7.7</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="42">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>96.5</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="43">
@@ -1283,11 +1283,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="45">
@@ -1323,11 +1323,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="46">
@@ -1343,11 +1343,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47">
@@ -1363,11 +1363,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>96.40000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="48">
@@ -1383,11 +1383,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>35.8</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="49">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="50">
@@ -1423,11 +1423,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="51">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="52">
@@ -1463,11 +1463,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="54">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="55">
@@ -1523,11 +1523,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -1543,11 +1543,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>97.5</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>40.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="59">
@@ -1603,11 +1603,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="60">
@@ -1623,11 +1623,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>33.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="61">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="62">
@@ -1663,11 +1663,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>97</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="63">
@@ -1683,11 +1683,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>38.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="64">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>27.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -1723,11 +1723,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="66">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="67">
@@ -1763,11 +1763,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68">
@@ -1783,11 +1783,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="69">
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="70">
@@ -1823,11 +1823,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>33.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="71">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1923,17 +1923,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25.9</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1943,17 +1943,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>35.5</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>25.9</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="82">
@@ -2063,11 +2063,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>96.90000000000001</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="83">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>40.7</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="84">
@@ -2103,11 +2103,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.8</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="85">
@@ -2123,11 +2123,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24.2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="86">
@@ -2143,11 +2143,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="87">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>96.3</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="88">
@@ -2183,11 +2183,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>38.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="89">
@@ -2203,11 +2203,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.9</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="90">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="91">
@@ -2243,11 +2243,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="92">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>97.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>43</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="94">
@@ -2303,11 +2303,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="95">
@@ -2323,11 +2323,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="96">
@@ -2343,11 +2343,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9.699999999999999</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="97">
@@ -2363,11 +2363,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>97.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="98">
@@ -2383,11 +2383,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>40.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="99">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="100">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>28.3</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="101">
@@ -2443,11 +2443,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="102">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -2483,11 +2483,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104">
@@ -2503,11 +2503,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="105">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>32.3</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="106">
@@ -2543,11 +2543,311 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Geladeira</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>97.40000000000001</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Máquina de lavar roupa</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Carro</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Motocicleta</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Carro e motocicleta</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Geladeira</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D112" t="n">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Máquina de lavar roupa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Carro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Motocicleta</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Carro e motocicleta</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
         <v>10.8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Geladeira</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Máquina de lavar roupa</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Carro</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Motocicleta</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Carro e motocicleta</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
